--- a/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-observationalcoholuse.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-observationalcoholuse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T13:57:28+00:00</t>
+    <t>2026-01-29T11:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-observationalcoholuse.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-observationalcoholuse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T11:52:07+00:00</t>
+    <t>2026-02-03T10:09:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
